--- a/ExcelFiles/WriteDataMultipleRowsAndCells.xlsx
+++ b/ExcelFiles/WriteDataMultipleRowsAndCells.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\QT_Selenium_228,229\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CB04E726824E2B3E0E64E90DCF289E84C52FB9BC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B1D6CD-F6A0-4520-B090-C210597F5B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3492" yWindow="1044" windowWidth="18996" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmpData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>EmpID</t>
   </si>
@@ -59,6 +59,15 @@
   </si>
   <si>
     <t>Finance</t>
+  </si>
+  <si>
+    <t>`25000</t>
+  </si>
+  <si>
+    <t>`30000</t>
+  </si>
+  <si>
+    <t>`35000</t>
   </si>
 </sst>
 </file>
@@ -410,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -437,11 +446,11 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>25000</v>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -451,11 +460,11 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>30000</v>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -465,8 +474,8 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="F4">
-        <v>35000</v>
+      <c r="D4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
